--- a/data/exports/王颖瑜伽/dist_order_2026-10-07.xlsx
+++ b/data/exports/王颖瑜伽/dist_order_2026-10-07.xlsx
@@ -259,7 +259,7 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>明天会更好</t>
+          <t>家乡的美</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
